--- a/forms/trg/Formulir_TRG_oilpalm.xlsx
+++ b/forms/trg/Formulir_TRG_oilpalm.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!B5:B33)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,41 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Syatrianty A. Syaiful</t>
+          <t>Prof. Dr. Ir. H. Nasaruddin</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Seed Physiology</t>
+          <t>Plant Physiology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0009-0003-5318-5870</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6024840</t>
+          <t>6016624</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>56938658300</t>
+          <t>57216823351</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Rafiuddin</t>
+          <t>Dr. Syatrianty A. Syaiful</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Plant Ecology</t>
+          <t>Seed Physiology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +978,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0897-0469</t>
+          <t>0009-0003-5318-5870</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6019697</t>
+          <t>6024840</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57202445262</t>
+          <t>56938658300</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1003,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mohd Hadi Akbar Bin Basri</t>
+          <t>Dr. Rafiuddin</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Department of Crop Sciences, Universiti Putra Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Oil Palm Agronomy</t>
+          <t>Plant Ecology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,13 +1027,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3541-9795</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0003-0897-0469</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6019697</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>56960019400</t>
+          <t>57202445262</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,22 +1052,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ts Dr. Siti Khairunniza Bejo</t>
+          <t>Dr. Mohd Hadi Akbar Bin Basri</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Institute of Plantation, Universiti Putra Malaysia</t>
+          <t>Department of Crop Sciences, Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Imaging Technology, Precision Agriculture &amp; Artificial Intelligence</t>
+          <t>Oil Palm Agronomy</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1080,13 +1076,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4972-1701</t>
+          <t>0000-0003-3541-9795</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>8394157300</t>
+          <t>56960019400</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1101,12 +1097,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>TS. DR. Anas Mohd Mustafah</t>
+          <t>Prof. Ts Dr. Siti Khairunniza Bejo</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1116,7 +1112,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Control and Automation, Agricultural Machinery Design and Control, Automation, Green Technology and Energy</t>
+          <t>Imaging Technology, Precision Agriculture &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1125,13 +1121,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8368-3035</t>
+          <t>0000-0002-4972-1701</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>56333327200</t>
+          <t>8394157300</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1146,12 +1142,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Madya Dr. Mohd Rafein Zakaria</t>
+          <t>TS. DR. Anas Mohd Mustafah</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1161,7 +1157,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Product Processing and Development</t>
+          <t>Control and Automation, Agricultural Machinery Design and Control, Automation, Green Technology and Energy</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1170,13 +1166,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2698-615X</t>
+          <t>0000-0001-8368-3035</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>55346979800</t>
+          <t>56333327200</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1191,22 +1187,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Muh. Farid BDR</t>
+          <t>Prof. Madya Dr. Mohd Rafein Zakaria</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Institute of Plantation, Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Plant Breeding</t>
+          <t>Product Processing and Development</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1215,17 +1211,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7178-7790</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>6022499</t>
-        </is>
-      </c>
+          <t>0000-0002-2698-615X</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57202443204</t>
+          <t>55346979800</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1240,12 +1232,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Kaimuddin</t>
+          <t>Prof. Muh. Farid BDR</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1255,7 +1247,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Agriculture Climatology</t>
+          <t>Plant Breeding</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1264,17 +1256,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4007-4007</t>
+          <t>0000-0002-7178-7790</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>6017645</t>
+          <t>6022499</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>59370123700</t>
+          <t>57202443204</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1289,12 +1281,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mahyuddin</t>
+          <t>Prof. Kaimuddin</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1304,16 +1296,28 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Agribusiness</t>
+          <t>Agriculture Climatology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4007-4007</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>6017645</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>59370123700</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Prof. Salengke</t>
+          <t>Dr. Mahyuddin</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1341,28 +1345,16 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Food Process Engineering</t>
+          <t>Agribusiness</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-7777-2971</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>5976145</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>6507093353</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1375,12 +1367,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Prof. Amran Laga</t>
+          <t>Prof. Salengke</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1390,7 +1382,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Food Biotechnology</t>
+          <t>Food Process Engineering</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1399,17 +1391,17 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5497-2388</t>
+          <t>0000-0001-7777-2971</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>6042439</t>
+          <t>5976145</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>57196148278</t>
+          <t>6507093353</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1424,12 +1416,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ifayanti Ridwan Saleh, Ph.D.</t>
+          <t>Prof. Amran Laga</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1439,7 +1431,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Plant Ecophysiology</t>
+          <t>Food Biotechnology</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1448,17 +1440,17 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9528-3151</t>
+          <t>0000-0002-5497-2388</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>6016263</t>
+          <t>6042439</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>57218717855</t>
+          <t>57196148278</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -1473,22 +1465,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Nurhasni Hasan, Ph.D., Apt</t>
+          <t>Ifayanti Ridwan Saleh, Ph.D.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Pharmacy, Hasanuddin University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Drug Delivery System</t>
+          <t>Plant Ecophysiology</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1497,17 +1489,17 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2785-7229</t>
+          <t>0000-0001-9528-3151</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>6690067</t>
+          <t>6016263</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>56600684900</t>
+          <t>57218717855</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1522,22 +1514,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Akram</t>
+          <t>Nurhasni Hasan, Ph.D., Apt</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Faculty of Pharmacy, Hasanuddin University</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Agrotechnology</t>
+          <t>Drug Delivery System</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1546,11 +1538,19 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-1727-3106</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+          <t>0000-0002-2785-7229</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>6690067</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>56600684900</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1563,29 +1563,33 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rispan Ady Idris</t>
+          <t>Muhammad Akram</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Sciences Doctoral Program, Hasanuddin University Graduate School</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Oil Palm Agronomy</t>
+          <t>Agrotechnology</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-1727-3106</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
@@ -1600,33 +1604,29 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Arfina Shalsabila</t>
+          <t>Muhammad Rispan Ady Idris</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Agricultural Sciences Doctoral Program, Hasanuddin University Graduate School</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Agrotechnology</t>
+          <t>Oil Palm Agronomy</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>0009-0008-8851-2583</t>
-        </is>
-      </c>
+      <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="11" t="inlineStr">
@@ -1639,18 +1639,42 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Arfina Shalsabila</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Agrotechnology</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-8851-2583</t>
+        </is>
+      </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1839,15 +1863,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
